--- a/data/trans_orig/IP31C_R_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31C_R_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,107 +720,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2198</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5436</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2464</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>683</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5840</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>13,22%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2464</t>
+          <t>2198</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>709</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5624</t>
+          <t>5648</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>7,23%</t>
         </is>
       </c>
     </row>
@@ -833,74 +833,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>34347</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>31109</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>35898</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>93,98%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>85,13%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,23%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>45279</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>41566</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>41707</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>38331</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>43488</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>94,42%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>86,78%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>156</t>
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>86986</t>
+          <t>75913</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>83826</t>
+          <t>72463</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>88774</t>
+          <t>77402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>36545</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>36545</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>36545</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>45279</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>45279</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>45279</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44171</t>
+          <t>41566</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44171</t>
+          <t>41566</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>44171</t>
+          <t>41566</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>89450</t>
+          <t>78111</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>89450</t>
+          <t>78111</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>89450</t>
+          <t>78111</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,107 +1063,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>14866</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>9803</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11081</t>
+          <t>22749</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>5928</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>2776</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22138</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>20616</t>
+          <t>20794</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13907</t>
+          <t>13922</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28968</t>
+          <t>28216</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -1176,107 +1176,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>250</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>152485</t>
+          <t>142176</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147314</t>
+          <t>134293</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>155655</t>
+          <t>147239</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>252</t>
+          <t>246</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>167253</t>
+          <t>138809</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>159821</t>
+          <t>133592</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>172008</t>
+          <t>141961</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
-          <t>499</t>
+          <t>496</t>
         </is>
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>319739</t>
+          <t>280986</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>311387</t>
+          <t>273564</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>326448</t>
+          <t>287858</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>95,39%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>158395</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>158395</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>158395</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>144737</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>144737</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>144737</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>340355</t>
+          <t>301780</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>340355</t>
+          <t>301780</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>340355</t>
+          <t>301780</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,107 +1406,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>18</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20433</t>
+          <t>15679</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13884</t>
+          <t>9422</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28393</t>
+          <t>24433</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>22889</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>15472</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21433</t>
+          <t>31810</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>34356</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25663</t>
+          <t>28020</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>46061</t>
+          <t>49725</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>13,27%</t>
         </is>
       </c>
     </row>
@@ -1519,107 +1519,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>225</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>152639</t>
+          <t>184447</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144679</t>
+          <t>175693</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>159188</t>
+          <t>190704</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>206</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>198567</t>
+          <t>151783</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>191057</t>
+          <t>142862</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>204154</t>
+          <t>159200</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>81,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>431</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>351207</t>
+          <t>336230</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>339502</t>
+          <t>325073</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>359900</t>
+          <t>346778</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,107 +1749,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21697</t>
+          <t>40573</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13868</t>
+          <t>30527</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>32570</t>
+          <t>53470</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34170</t>
+          <t>30711</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23552</t>
+          <t>22459</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45451</t>
+          <t>44083</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>83</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>55867</t>
+          <t>71284</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42571</t>
+          <t>56891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>71281</t>
+          <t>87045</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -1862,107 +1862,107 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>292</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>252570</t>
+          <t>250786</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>241697</t>
+          <t>237889</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>260399</t>
+          <t>260832</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>306</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>270020</t>
+          <t>224626</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>258739</t>
+          <t>211254</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>280638</t>
+          <t>232878</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>598</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>522591</t>
+          <t>475412</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>507177</t>
+          <t>459651</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>535887</t>
+          <t>489805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>89,59%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>291359</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>291359</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>291359</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>274267</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>274267</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>274267</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304190</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>578458</t>
+          <t>546696</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>578458</t>
+          <t>546696</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>578458</t>
+          <t>546696</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,107 +2092,107 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>95</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>48040</t>
+          <t>73317</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36228</t>
+          <t>60289</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>61083</t>
+          <t>90234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>65264</t>
+          <t>59528</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52179</t>
+          <t>46171</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>80544</t>
+          <t>73643</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>167</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>113304</t>
+          <t>132844</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96021</t>
+          <t>113299</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134031</t>
+          <t>153988</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -2205,107 +2205,107 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>842</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>602974</t>
+          <t>611755</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>589931</t>
+          <t>594838</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>614786</t>
+          <t>624783</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>839</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>677547</t>
+          <t>556785</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>662267</t>
+          <t>542670</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>690632</t>
+          <t>570142</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>1700</t>
+          <t>1681</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1280521</t>
+          <t>1168540</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1259794</t>
+          <t>1147396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1297804</t>
+          <t>1188085</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>91,29%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>685072</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>911</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>651014</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>937</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>742811</t>
+          <t>616313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1393825</t>
+          <t>1301384</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
